--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0.333333</v>
+        <v>0.142857</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.333333</v>
+        <v>0.285714</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0.333333</v>
+        <v>0.142857</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.333333</v>
+        <v>0.285714</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.333333</v>
+        <v>0.142857</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6024,10 +6024,10 @@
         <v>0.699244</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.666667</v>
+        <v>0.285714</v>
       </c>
       <c r="J130" t="n">
         <v>1</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0.333333</v>
+        <v>0.142857</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>0.285714</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0.333333</v>
+        <v>0.142857</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
@@ -6973,7 +6973,7 @@
         <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.666667</v>
+        <v>0.714286</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0.333333</v>
+        <v>0.285714</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J154" t="n">
         <v>1</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>0.285714</v>
       </c>
       <c r="J157" t="n">
         <v>1</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -7446,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0.333333</v>
+        <v>0.142857</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0.333333</v>
+        <v>0.285714</v>
       </c>
       <c r="J164" t="n">
         <v>1</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J166" t="n">
         <v>1</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J167" t="n">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>0.285714</v>
       </c>
       <c r="J168" t="n">
         <v>1</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J169" t="n">
         <v>1</v>
@@ -7790,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J171" t="n">
         <v>1</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J172" t="n">
         <v>1</v>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -8005,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J176" t="n">
         <v>1</v>
@@ -8220,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>0.285714</v>
       </c>
       <c r="J181" t="n">
         <v>1</v>
@@ -8392,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J185" t="n">
         <v>1</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J191" t="n">
         <v>1</v>
@@ -8736,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>0.285714</v>
       </c>
       <c r="J193" t="n">
         <v>1</v>
@@ -8779,7 +8779,7 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J194" t="n">
         <v>1</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>0.285714</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>0.428571</v>
       </c>
       <c r="J198" t="n">
         <v>1</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0.333333</v>
+        <v>0.142857</v>
       </c>
       <c r="J199" t="n">
         <v>1</v>
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J200" t="n">
         <v>1</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>0.333333</v>
+        <v>0.285714</v>
       </c>
       <c r="J201" t="n">
         <v>1</v>
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
@@ -14065,10 +14065,10 @@
         <v>0.16562</v>
       </c>
       <c r="H317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I317" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -14111,7 +14111,7 @@
         <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J318" t="n">
         <v>1</v>
@@ -14538,10 +14538,10 @@
         <v>0.82774</v>
       </c>
       <c r="H328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J328" t="n">
         <v>1</v>
@@ -14885,7 +14885,7 @@
         <v>0</v>
       </c>
       <c r="I336" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J336" t="n">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J346" t="n">
         <v>1</v>
@@ -15398,10 +15398,10 @@
         <v>0.512563</v>
       </c>
       <c r="H348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I348" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J348" t="n">
         <v>0</v>
@@ -15487,7 +15487,7 @@
         <v>0</v>
       </c>
       <c r="I350" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J350" t="n">
         <v>1</v>
@@ -15527,10 +15527,10 @@
         <v>0.665069</v>
       </c>
       <c r="H351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
@@ -15573,7 +15573,7 @@
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J352" t="n">
         <v>0</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="I367" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
@@ -16476,7 +16476,7 @@
         <v>0</v>
       </c>
       <c r="I373" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J373" t="n">
         <v>0</v>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J375" t="n">
         <v>0</v>
@@ -17333,10 +17333,10 @@
         <v>0.509704</v>
       </c>
       <c r="H393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I393" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J393" t="n">
         <v>1</v>
@@ -17422,7 +17422,7 @@
         <v>0</v>
       </c>
       <c r="I395" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J395" t="n">
         <v>1</v>
@@ -17935,10 +17935,10 @@
         <v>0.862943</v>
       </c>
       <c r="H407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I407" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J407" t="n">
         <v>1</v>
@@ -18153,7 +18153,7 @@
         <v>0</v>
       </c>
       <c r="I412" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J412" t="n">
         <v>1</v>
@@ -18236,10 +18236,10 @@
         <v>0.943173</v>
       </c>
       <c r="H414" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I414" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J414" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4943,10 +4943,10 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.522798</v>
+        <v>0.363098</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.122254</v>
+        <v>0.161173</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.172699</v>
+        <v>0.189665</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.986713</v>
+        <v>0.99614</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.225457</v>
+        <v>0.199612</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.913685</v>
+        <v>0.920412</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.070109</v>
+        <v>0.167462</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.228586</v>
+        <v>0.164946</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.22479</v>
+        <v>0.22093</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.270695</v>
+        <v>0.23899</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.31787</v>
+        <v>0.264497</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.306541</v>
+        <v>0.263405</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0.735699</v>
+        <v>0.661959</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.286003</v>
+        <v>0.262551</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5545,10 +5545,10 @@
         <v>0.89211</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.541381</v>
+        <v>0.454046</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.244289</v>
+        <v>0.181728</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.377244</v>
+        <v>0.328406</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.790843</v>
+        <v>0.773077</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.413786</v>
+        <v>0.367255</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.195519</v>
+        <v>0.205243</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.275232</v>
+        <v>0.247108</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.310507</v>
+        <v>0.224486</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.130034</v>
+        <v>0.107823</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.286743</v>
+        <v>0.208037</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.581846</v>
+        <v>0.5813430000000001</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.699244</v>
+        <v>0.56393</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.238014</v>
+        <v>0.215538</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.273792</v>
+        <v>0.208234</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.232379</v>
+        <v>0.259568</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.183285</v>
+        <v>0.215473</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.30587</v>
+        <v>0.285846</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.201233</v>
+        <v>0.186452</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.281519</v>
+        <v>0.221752</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.18332</v>
+        <v>0.143539</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.356786</v>
+        <v>0.282634</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.208371</v>
+        <v>0.196599</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.253466</v>
+        <v>0.184907</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.306608</v>
+        <v>0.245266</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.377774</v>
+        <v>0.303712</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.435484</v>
+        <v>0.431552</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.317003</v>
+        <v>0.264144</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6706,10 +6706,10 @@
         <v>0.025875</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.657184</v>
+        <v>0.440372</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6749,10 +6749,10 @@
         <v>0.124282</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0.47689</v>
+        <v>0.504217</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.206483</v>
+        <v>0.227848</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.407707</v>
+        <v>0.35543</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.123837</v>
+        <v>0.188713</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.825101</v>
+        <v>0.874858</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.9973379999999999</v>
+        <v>0.999296</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.22757</v>
+        <v>0.183118</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7050,10 +7050,10 @@
         <v>6e-06</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.55152</v>
+        <v>0.49235</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.260442</v>
+        <v>0.308744</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7136,10 +7136,10 @@
         <v>1e-06</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.541629</v>
+        <v>0.399572</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0.776375</v>
+        <v>0.736945</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.462539</v>
+        <v>0.362444</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.251433</v>
+        <v>0.198602</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.222259</v>
+        <v>0.194139</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.199266</v>
+        <v>0.206061</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.372817</v>
+        <v>0.282109</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.91918</v>
+        <v>0.900331</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.231851</v>
+        <v>0.247299</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.173931</v>
+        <v>0.208542</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.555146</v>
+        <v>0.559072</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.179704</v>
+        <v>0.184007</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.363036</v>
+        <v>0.433057</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.188109</v>
+        <v>0.210146</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.18835</v>
+        <v>0.215729</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.353238</v>
+        <v>0.361338</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>0.506405</v>
+        <v>0.603512</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.144097</v>
+        <v>0.186842</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.102888</v>
+        <v>0.118658</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.293333</v>
+        <v>0.256832</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0.557454</v>
+        <v>0.507996</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.169235</v>
+        <v>0.162055</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.318731</v>
+        <v>0.267203</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.127562</v>
+        <v>0.145962</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.104757</v>
+        <v>0.123721</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.436432</v>
+        <v>0.356403</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8254,10 +8254,10 @@
         <v>0.003401</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.516402</v>
+        <v>0.47245</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.105785</v>
+        <v>0.118076</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.143805</v>
+        <v>0.165529</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.199342</v>
+        <v>0.147538</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.138183</v>
+        <v>0.158785</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.390103</v>
+        <v>0.340502</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.48161</v>
+        <v>0.402493</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.316385</v>
+        <v>0.255619</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8598,10 +8598,10 @@
         <v>0.024671</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.641743</v>
+        <v>0.390851</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.45311</v>
+        <v>0.431061</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>0.545022</v>
+        <v>0.569613</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.606448</v>
+        <v>0.570503</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.265766</v>
+        <v>0.257716</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.262429</v>
+        <v>0.243731</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.325835</v>
+        <v>0.354472</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.8974569999999999</v>
+        <v>0.918235</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.915615</v>
+        <v>0.966385</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.6531400000000001</v>
+        <v>0.654069</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9028,10 +9028,10 @@
         <v>0.001694</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.5987</v>
+        <v>0.455553</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="G201" t="n">
-        <v>0.54287</v>
+        <v>0.5208</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
